--- a/options_trades_dummy.xlsx
+++ b/options_trades_dummy.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="33">
   <si>
     <t>TradeID</t>
   </si>
@@ -82,12 +82,18 @@
     <t>O010</t>
   </si>
   <si>
-    <t>BRN Sep26</t>
+    <t>O011</t>
+  </si>
+  <si>
+    <t>O012</t>
   </si>
   <si>
     <t>BRN Oct26</t>
   </si>
   <si>
+    <t>BRN Nov26</t>
+  </si>
+  <si>
     <t>BRN Dec26</t>
   </si>
   <si>
@@ -103,7 +109,7 @@
     <t>SELL</t>
   </si>
   <si>
-    <t>Rayane</t>
+    <t>Dummy</t>
   </si>
   <si>
     <t>USD</t>
@@ -442,7 +448,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
@@ -488,37 +494,37 @@
         <v>12</v>
       </c>
       <c r="B2" s="1">
-        <v>46210</v>
+        <v>46205</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F2" s="1">
-        <v>46280</v>
+        <v>46260</v>
       </c>
       <c r="G2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H2">
         <v>10</v>
       </c>
       <c r="I2">
-        <v>1.85</v>
+        <v>2.23</v>
       </c>
       <c r="J2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K2">
         <v>1000</v>
       </c>
       <c r="L2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -526,37 +532,37 @@
         <v>13</v>
       </c>
       <c r="B3" s="1">
-        <v>46212</v>
+        <v>46209</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E3">
-        <v>80</v>
+        <v>76.5</v>
       </c>
       <c r="F3" s="1">
-        <v>46280</v>
+        <v>46260</v>
       </c>
       <c r="G3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H3">
         <v>8</v>
       </c>
       <c r="I3">
-        <v>1.4</v>
+        <v>2.05</v>
       </c>
       <c r="J3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K3">
         <v>1000</v>
       </c>
       <c r="L3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -564,37 +570,37 @@
         <v>14</v>
       </c>
       <c r="B4" s="1">
-        <v>46214</v>
+        <v>46211</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E4">
-        <v>83</v>
+        <v>79.5</v>
       </c>
       <c r="F4" s="1">
-        <v>46295</v>
+        <v>46290</v>
       </c>
       <c r="G4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H4">
         <v>6</v>
       </c>
       <c r="I4">
-        <v>1.55</v>
+        <v>4.54</v>
       </c>
       <c r="J4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K4">
         <v>1000</v>
       </c>
       <c r="L4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -602,37 +608,37 @@
         <v>15</v>
       </c>
       <c r="B5" s="1">
-        <v>46217</v>
+        <v>46213</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D5" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E5">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="F5" s="1">
-        <v>46280</v>
+        <v>46322</v>
       </c>
       <c r="G5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H5">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I5">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="J5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K5">
         <v>1000</v>
       </c>
       <c r="L5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -640,37 +646,37 @@
         <v>16</v>
       </c>
       <c r="B6" s="1">
-        <v>46219</v>
+        <v>46217</v>
       </c>
       <c r="C6" t="s">
         <v>24</v>
       </c>
       <c r="D6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E6">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="F6" s="1">
-        <v>46310</v>
+        <v>46260</v>
       </c>
       <c r="G6" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="H6">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I6">
-        <v>1.7</v>
+        <v>0.53</v>
       </c>
       <c r="J6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K6">
         <v>1000</v>
       </c>
       <c r="L6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -678,37 +684,37 @@
         <v>17</v>
       </c>
       <c r="B7" s="1">
-        <v>46221</v>
+        <v>46219</v>
       </c>
       <c r="C7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D7" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E7">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="F7" s="1">
-        <v>46295</v>
+        <v>46290</v>
       </c>
       <c r="G7" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I7">
-        <v>1.75</v>
+        <v>2.27</v>
       </c>
       <c r="J7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K7">
         <v>1000</v>
       </c>
       <c r="L7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -716,37 +722,37 @@
         <v>18</v>
       </c>
       <c r="B8" s="1">
-        <v>46224</v>
+        <v>46223</v>
       </c>
       <c r="C8" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E8">
-        <v>80</v>
+        <v>77.5</v>
       </c>
       <c r="F8" s="1">
-        <v>46280</v>
+        <v>46322</v>
       </c>
       <c r="G8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H8">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I8">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="J8" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K8">
         <v>1000</v>
       </c>
       <c r="L8" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -754,37 +760,37 @@
         <v>19</v>
       </c>
       <c r="B9" s="1">
-        <v>46226</v>
+        <v>46225</v>
       </c>
       <c r="C9" t="s">
         <v>24</v>
       </c>
       <c r="D9" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E9">
-        <v>82</v>
+        <v>76.5</v>
       </c>
       <c r="F9" s="1">
-        <v>46310</v>
+        <v>46260</v>
       </c>
       <c r="G9" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="H9">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I9">
-        <v>1.6</v>
+        <v>5.44</v>
       </c>
       <c r="J9" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K9">
         <v>1000</v>
       </c>
       <c r="L9" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -792,37 +798,37 @@
         <v>20</v>
       </c>
       <c r="B10" s="1">
-        <v>46230</v>
+        <v>46227</v>
       </c>
       <c r="C10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E10">
-        <v>79</v>
+        <v>79.5</v>
       </c>
       <c r="F10" s="1">
-        <v>46310</v>
+        <v>46290</v>
       </c>
       <c r="G10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I10">
-        <v>1.55</v>
+        <v>0.96</v>
       </c>
       <c r="J10" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K10">
         <v>1000</v>
       </c>
       <c r="L10" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -830,37 +836,113 @@
         <v>21</v>
       </c>
       <c r="B11" s="1">
+        <v>46230</v>
+      </c>
+      <c r="C11" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" t="s">
+        <v>28</v>
+      </c>
+      <c r="E11">
+        <v>67.5</v>
+      </c>
+      <c r="F11" s="1">
+        <v>46322</v>
+      </c>
+      <c r="G11" t="s">
+        <v>29</v>
+      </c>
+      <c r="H11">
+        <v>6</v>
+      </c>
+      <c r="I11">
+        <v>2.44</v>
+      </c>
+      <c r="J11" t="s">
+        <v>31</v>
+      </c>
+      <c r="K11">
+        <v>1000</v>
+      </c>
+      <c r="L11" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="A12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" s="1">
+        <v>46231</v>
+      </c>
+      <c r="C12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D12" t="s">
+        <v>27</v>
+      </c>
+      <c r="E12">
+        <v>69.5</v>
+      </c>
+      <c r="F12" s="1">
+        <v>46322</v>
+      </c>
+      <c r="G12" t="s">
+        <v>29</v>
+      </c>
+      <c r="H12">
+        <v>4</v>
+      </c>
+      <c r="I12">
+        <v>3.91</v>
+      </c>
+      <c r="J12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K12">
+        <v>1000</v>
+      </c>
+      <c r="L12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="A13" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" s="1">
         <v>46233</v>
       </c>
-      <c r="C11" t="s">
-        <v>23</v>
-      </c>
-      <c r="D11" t="s">
-        <v>26</v>
-      </c>
-      <c r="E11">
-        <v>80</v>
-      </c>
-      <c r="F11" s="1">
-        <v>46295</v>
-      </c>
-      <c r="G11" t="s">
-        <v>27</v>
-      </c>
-      <c r="H11">
-        <v>7</v>
-      </c>
-      <c r="I11">
-        <v>1.3</v>
-      </c>
-      <c r="J11" t="s">
-        <v>29</v>
-      </c>
-      <c r="K11">
-        <v>1000</v>
-      </c>
-      <c r="L11" t="s">
+      <c r="C13" t="s">
+        <v>25</v>
+      </c>
+      <c r="D13" t="s">
+        <v>28</v>
+      </c>
+      <c r="E13">
+        <v>74.5</v>
+      </c>
+      <c r="F13" s="1">
+        <v>46290</v>
+      </c>
+      <c r="G13" t="s">
         <v>30</v>
+      </c>
+      <c r="H13">
+        <v>3</v>
+      </c>
+      <c r="I13">
+        <v>5.31</v>
+      </c>
+      <c r="J13" t="s">
+        <v>31</v>
+      </c>
+      <c r="K13">
+        <v>1000</v>
+      </c>
+      <c r="L13" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
